--- a/schedule_explorer.xlsx
+++ b/schedule_explorer.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fredbuckhold/Documents/Project Z/Project Z v.2/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fredbuckhold/Documents/Project Z v.2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1C11F15E-95C6-7944-9E18-D59B113E69CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5247A666-CEDF-A441-ADC3-23C3C6C1C8C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10520" yWindow="660" windowWidth="24040" windowHeight="20200" activeTab="3" xr2:uid="{9751DBBB-1B34-9544-AB25-55F1DA5D89E9}"/>
+    <workbookView xWindow="10520" yWindow="660" windowWidth="24040" windowHeight="20200" activeTab="1" xr2:uid="{9751DBBB-1B34-9544-AB25-55F1DA5D89E9}"/>
   </bookViews>
   <sheets>
     <sheet name="Daily assignment" sheetId="1" r:id="rId1"/>
